--- a/feedback_forms/041_friend_roast_feedback_form--feedback_forms.xlsx
+++ b/feedback_forms/041_friend_roast_feedback_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>self_deprecating</t>
+          <t>self deprecating</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>thought_provoking</t>
+          <t>thought provoking</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>not at all</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>liked_it</t>
+          <t>liked it</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>did_not_like</t>
+          <t>did not like</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>liked_it_a_lot</t>
+          <t>liked it a lot</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>would_really_like_to_hav</t>
+          <t>would really like to hav</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>would_like_to_repeat</t>
+          <t>would like to repeat</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>would_not_like_to_repeat</t>
+          <t>would not like to repeat</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>not at all</t>
         </is>
       </c>
     </row>
